--- a/crates/forskscope-core/src/tests/fixtures/xlsx/formula/old.xlsx
+++ b/crates/forskscope-core/src/tests/fixtures/xlsx/formula/old.xlsx
@@ -340,11 +340,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1">
+    <row r="1" spans="1:1">
+      <c r="A1">
         <f>1+1</f>
         <v>0</v>
       </c>
